--- a/主动DAU与社区首页UV数据.xlsx
+++ b/主动DAU与社区首页UV数据.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C219"/>
+  <dimension ref="A1:C553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -467,2834 +467,7176 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>990914</v>
+        <v>544800</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4054</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1012612</v>
+        <v>792680</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4254</v>
+        <v>3526</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1010840</v>
+        <v>789820</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>4373</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1006405</v>
+        <v>544473</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4042</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-01-05</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>981577</v>
+        <v>413526</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3749</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>723677</v>
+        <v>772581</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2550</v>
+        <v>3313</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>560746</v>
+        <v>799389</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>2252</v>
+        <v>3301</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>979486</v>
+        <v>781760</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3783</v>
+        <v>3449</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1001761</v>
+        <v>770215</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4081</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1012719</v>
+        <v>775461</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>4218</v>
+        <v>3293</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-01-11</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1034741</v>
+        <v>544140</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>4788</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-01-12</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>994479</v>
+        <v>413743</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>4177</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>762590</v>
+        <v>756405</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>2844</v>
+        <v>3092</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>571768</v>
+        <v>799650</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2292</v>
+        <v>3304</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>971913</v>
+        <v>778542</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>4154</v>
+        <v>3381</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1020486</v>
+        <v>773145</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>4667</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>1013829</v>
+        <v>772552</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>4344</v>
+        <v>2937</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>1018149</v>
+        <v>550685</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>4680</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1000679</v>
+        <v>457406</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>4295</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>727651</v>
+        <v>774518</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>2554</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>550088</v>
+        <v>800902</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2352</v>
+        <v>3405</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>974857</v>
+        <v>780916</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>4273</v>
+        <v>3232</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>1016848</v>
+        <v>771261</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>4640</v>
+        <v>3069</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1012670</v>
+        <v>753028</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>4760</v>
+        <v>3027</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2025-01-25</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>987369</v>
+        <v>542327</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>4259</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>975070</v>
+        <v>469767</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>4513</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>736971</v>
+        <v>696674</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>3320</v>
+        <v>2725</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>582533</v>
+        <v>560615</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2933</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>1022159</v>
+        <v>543726</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>5602</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>1032078</v>
+        <v>563296</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>5284</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>984399</v>
+        <v>546114</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>4537</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>697434</v>
+        <v>534564</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>2671</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>738751</v>
+        <v>457178</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>3367</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>763515</v>
+        <v>607155</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>3456</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>777600</v>
+        <v>654005</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>3539</v>
+        <v>2644</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>1050682</v>
+        <v>812428</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>4920</v>
+        <v>3365</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>1064749</v>
+        <v>800234</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>5003</v>
+        <v>3217</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>1064528</v>
+        <v>802439</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>5242</v>
+        <v>3381</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>1055436</v>
+        <v>664698</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>5216</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-02-09</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>1049381</v>
+        <v>471292</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>5024</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>783241</v>
+        <v>799566</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>3538</v>
+        <v>3199</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>618151</v>
+        <v>820473</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>3065</v>
+        <v>3392</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>1077513</v>
+        <v>809134</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>5282</v>
+        <v>3283</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>1107598</v>
+        <v>817723</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>5708</v>
+        <v>3431</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>1116877</v>
+        <v>815810</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>5823</v>
+        <v>3355</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-02-15</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>1117369</v>
+        <v>604603</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>5957</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-02-16</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1061788</v>
+        <v>500232</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>5184</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>782239</v>
+        <v>820429</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>3332</v>
+        <v>3435</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>639477</v>
+        <v>840217</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>3088</v>
+        <v>3522</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>1039566</v>
+        <v>828186</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>4897</v>
+        <v>3415</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>1080996</v>
+        <v>833199</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>5209</v>
+        <v>3562</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>1097765</v>
+        <v>833023</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>5843</v>
+        <v>3359</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>1090907</v>
+        <v>626342</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>5831</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-02-23</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>1081513</v>
+        <v>499131</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>5975</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>819534</v>
+        <v>826740</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>4080</v>
+        <v>3486</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>648203</v>
+        <v>845407</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>3577</v>
+        <v>3669</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>1089991</v>
+        <v>855935</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>6180</v>
+        <v>3697</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>1110726</v>
+        <v>850153</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>6919</v>
+        <v>3801</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>1160277</v>
+        <v>852779</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>7889</v>
+        <v>3947</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>1228498</v>
+        <v>629843</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>10498</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>1262245</v>
+        <v>500996</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>12674</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>1061808</v>
+        <v>831663</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>9406</v>
+        <v>3603</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>834449</v>
+        <v>875315</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>6280</v>
+        <v>3927</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>1317266</v>
+        <v>859738</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>12382</v>
+        <v>3775</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>1276626</v>
+        <v>870389</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>9864</v>
+        <v>3926</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>1268744</v>
+        <v>839589</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>9345</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>1262299</v>
+        <v>623282</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>9713</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>1228655</v>
+        <v>490196</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>8675</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>959856</v>
+        <v>821197</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>4773</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>704573</v>
+        <v>886003</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>3529</v>
+        <v>4121</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>1148995</v>
+        <v>871327</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>6321</v>
+        <v>3827</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>1148909</v>
+        <v>864193</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>6006</v>
+        <v>3836</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>1136855</v>
+        <v>864201</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>5870</v>
+        <v>3713</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>1108698</v>
+        <v>666877</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>5171</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>1087050</v>
+        <v>517953</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>5478</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>836545</v>
+        <v>833089</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>3099</v>
+        <v>3489</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>628715</v>
+        <v>864203</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>2317</v>
+        <v>3744</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>739366</v>
+        <v>849583</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>2711</v>
+        <v>3679</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>785085</v>
+        <v>852617</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>3106</v>
+        <v>4039</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>785266</v>
+        <v>841864</v>
       </c>
       <c r="C81" s="3" t="n">
-        <v>3110</v>
+        <v>3559</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>781480</v>
+        <v>607009</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>3235</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>804540</v>
+        <v>472357</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>3451</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>790059</v>
+        <v>819150</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>3086</v>
+        <v>3351</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>640467</v>
+        <v>834182</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>2391</v>
+        <v>3432</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>903843</v>
+        <v>828955</v>
       </c>
       <c r="C86" s="3" t="n">
-        <v>4369</v>
+        <v>3422</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>1162268</v>
+        <v>821771</v>
       </c>
       <c r="C87" s="3" t="n">
-        <v>5748</v>
+        <v>3615</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>1167330</v>
+        <v>825642</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>5453</v>
+        <v>3485</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>1174942</v>
+        <v>606867</v>
       </c>
       <c r="C89" s="3" t="n">
-        <v>5961</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>1183555</v>
+        <v>470287</v>
       </c>
       <c r="C90" s="3" t="n">
-        <v>5895</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>1161031</v>
+        <v>818190</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>6225</v>
+        <v>3626</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>1013315</v>
+        <v>839150</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>5611</v>
+        <v>3589</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="B93" s="3" t="n">
-        <v>1347844</v>
+        <v>837608</v>
       </c>
       <c r="C93" s="3" t="n">
-        <v>8387</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>1351006</v>
+        <v>900847</v>
       </c>
       <c r="C94" s="3" t="n">
-        <v>8262</v>
+        <v>5145</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="B95" s="3" t="n">
-        <v>1341788</v>
+        <v>769576</v>
       </c>
       <c r="C95" s="3" t="n">
-        <v>8010</v>
+        <v>4138</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>1299978</v>
+        <v>725568</v>
       </c>
       <c r="C96" s="3" t="n">
-        <v>7139</v>
+        <v>3357</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="B97" s="3" t="n">
-        <v>1274324</v>
+        <v>585631</v>
       </c>
       <c r="C97" s="3" t="n">
-        <v>6838</v>
+        <v>2645</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>1004620</v>
+        <v>1089378</v>
       </c>
       <c r="C98" s="3" t="n">
-        <v>4472</v>
+        <v>7850</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>783047</v>
+        <v>1066170</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>3627</v>
+        <v>6426</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>1287956</v>
+        <v>1095995</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>7218</v>
+        <v>7666</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>1294487</v>
+        <v>1110255</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>6945</v>
+        <v>7557</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>1288497</v>
+        <v>1055207</v>
       </c>
       <c r="C102" s="3" t="n">
-        <v>6632</v>
+        <v>6143</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>1285044</v>
+        <v>812221</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>6279</v>
+        <v>3580</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>1268924</v>
+        <v>619708</v>
       </c>
       <c r="C104" s="3" t="n">
-        <v>6259</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="B105" s="3" t="n">
-        <v>982524</v>
+        <v>963291</v>
       </c>
       <c r="C105" s="3" t="n">
-        <v>4376</v>
+        <v>4495</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>801533</v>
+        <v>959383</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>3737</v>
+        <v>4264</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>1267504</v>
+        <v>990177</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>6293</v>
+        <v>4821</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>1270361</v>
+        <v>967287</v>
       </c>
       <c r="C108" s="3" t="n">
-        <v>5864</v>
+        <v>4519</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="B109" s="3" t="n">
-        <v>1286717</v>
+        <v>929618</v>
       </c>
       <c r="C109" s="3" t="n">
-        <v>6561</v>
+        <v>3684</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>1347459</v>
+        <v>609826</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>8092</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>1305185</v>
+        <v>539904</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>6796</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>1005247</v>
+        <v>930061</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>4688</v>
+        <v>4183</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="B113" s="3" t="n">
-        <v>842322</v>
+        <v>964980</v>
       </c>
       <c r="C113" s="3" t="n">
-        <v>4072</v>
+        <v>4634</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>1431359</v>
+        <v>988748</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>9629</v>
+        <v>5024</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>1402543</v>
+        <v>962250</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>7913</v>
+        <v>4651</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>1362207</v>
+        <v>928133</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>6915</v>
+        <v>4209</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="B117" s="3" t="n">
-        <v>1337357</v>
+        <v>710264</v>
       </c>
       <c r="C117" s="3" t="n">
-        <v>6432</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>1323689</v>
+        <v>612076</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>6018</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="B119" s="3" t="n">
-        <v>1024829</v>
+        <v>879764</v>
       </c>
       <c r="C119" s="3" t="n">
-        <v>4035</v>
+        <v>3777</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>810717</v>
+        <v>878841</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>3380</v>
+        <v>3621</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>1294899</v>
+        <v>873457</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>5926</v>
+        <v>3490</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>1305405</v>
+        <v>707474</v>
       </c>
       <c r="C122" s="3" t="n">
-        <v>5518</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>1324127</v>
+        <v>708904</v>
       </c>
       <c r="C123" s="3" t="n">
-        <v>5994</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>1331661</v>
+        <v>647456</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>6306</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>1266079</v>
+        <v>503527</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>4905</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>857954</v>
+        <v>716065</v>
       </c>
       <c r="C126" s="3" t="n">
-        <v>2961</v>
+        <v>2984</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="B127" s="3" t="n">
-        <v>747474</v>
+        <v>919857</v>
       </c>
       <c r="C127" s="3" t="n">
-        <v>2839</v>
+        <v>3955</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>1015920</v>
+        <v>955578</v>
       </c>
       <c r="C128" s="3" t="n">
-        <v>4259</v>
+        <v>4458</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="B129" s="3" t="n">
-        <v>1306284</v>
+        <v>944984</v>
       </c>
       <c r="C129" s="3" t="n">
-        <v>5524</v>
+        <v>4415</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>1409776</v>
+        <v>899014</v>
       </c>
       <c r="C130" s="3" t="n">
-        <v>6730</v>
+        <v>3981</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="B131" s="3" t="n">
-        <v>1352125</v>
+        <v>679663</v>
       </c>
       <c r="C131" s="3" t="n">
-        <v>5922</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>1297181</v>
+        <v>524601</v>
       </c>
       <c r="C132" s="3" t="n">
-        <v>5038</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="B133" s="3" t="n">
-        <v>987708</v>
+        <v>977029</v>
       </c>
       <c r="C133" s="3" t="n">
-        <v>3490</v>
+        <v>4585</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>905167</v>
+        <v>955694</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>3873</v>
+        <v>4222</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>1311431</v>
+        <v>932138</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>5479</v>
+        <v>4075</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="B136" s="3" t="n">
-        <v>1295368</v>
+        <v>925377</v>
       </c>
       <c r="C136" s="3" t="n">
-        <v>5018</v>
+        <v>4347</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="B137" s="3" t="n">
-        <v>1292279</v>
+        <v>888694</v>
       </c>
       <c r="C137" s="3" t="n">
-        <v>4893</v>
+        <v>3763</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="B138" s="3" t="n">
-        <v>1280175</v>
+        <v>633570</v>
       </c>
       <c r="C138" s="3" t="n">
-        <v>4656</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="B139" s="3" t="n">
-        <v>1284058</v>
+        <v>514205</v>
       </c>
       <c r="C139" s="3" t="n">
-        <v>4877</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="B140" s="3" t="n">
-        <v>1039217</v>
+        <v>862671</v>
       </c>
       <c r="C140" s="3" t="n">
-        <v>3582</v>
+        <v>3656</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="B141" s="3" t="n">
-        <v>817110</v>
+        <v>868400</v>
       </c>
       <c r="C141" s="3" t="n">
-        <v>3125</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="B142" s="3" t="n">
-        <v>1272666</v>
+        <v>873972</v>
       </c>
       <c r="C142" s="3" t="n">
-        <v>4847</v>
+        <v>3587</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="B143" s="3" t="n">
-        <v>1284351</v>
+        <v>896911</v>
       </c>
       <c r="C143" s="3" t="n">
-        <v>4901</v>
+        <v>3961</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="B144" s="3" t="n">
-        <v>1270675</v>
+        <v>882903</v>
       </c>
       <c r="C144" s="3" t="n">
-        <v>4877</v>
+        <v>3828</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-05-24</t>
         </is>
       </c>
       <c r="B145" s="3" t="n">
-        <v>1267728</v>
+        <v>622885</v>
       </c>
       <c r="C145" s="3" t="n">
-        <v>5031</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="B146" s="3" t="n">
-        <v>1263222</v>
+        <v>461296</v>
       </c>
       <c r="C146" s="3" t="n">
-        <v>5043</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="B147" s="3" t="n">
-        <v>916309</v>
+        <v>834313</v>
       </c>
       <c r="C147" s="3" t="n">
-        <v>2871</v>
+        <v>3489</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="B148" s="3" t="n">
-        <v>768172</v>
+        <v>853914</v>
       </c>
       <c r="C148" s="3" t="n">
-        <v>2690</v>
+        <v>3539</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="B149" s="3" t="n">
-        <v>1208252</v>
+        <v>848243</v>
       </c>
       <c r="C149" s="3" t="n">
-        <v>4610</v>
+        <v>3645</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="B150" s="3" t="n">
-        <v>1240181</v>
+        <v>880549</v>
       </c>
       <c r="C150" s="3" t="n">
-        <v>4630</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="B151" s="3" t="n">
-        <v>1234415</v>
+        <v>847388</v>
       </c>
       <c r="C151" s="3" t="n">
-        <v>4429</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="B152" s="3" t="n">
-        <v>1202546</v>
+        <v>595283</v>
       </c>
       <c r="C152" s="3" t="n">
-        <v>4155</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B153" s="3" t="n">
-        <v>906841</v>
+        <v>459227</v>
       </c>
       <c r="C153" s="3" t="n">
-        <v>2796</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="B154" s="3" t="n">
-        <v>815379</v>
+        <v>702445</v>
       </c>
       <c r="C154" s="3" t="n">
-        <v>2263</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="B155" s="3" t="n">
-        <v>670309</v>
+        <v>853938</v>
       </c>
       <c r="C155" s="3" t="n">
-        <v>1934</v>
+        <v>3681</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="B156" s="3" t="n">
-        <v>900993</v>
+        <v>849191</v>
       </c>
       <c r="C156" s="3" t="n">
-        <v>2981</v>
+        <v>3541</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="B157" s="3" t="n">
-        <v>998869</v>
+        <v>874423</v>
       </c>
       <c r="C157" s="3" t="n">
-        <v>3227</v>
+        <v>3933</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="B158" s="3" t="n">
-        <v>1256736</v>
+        <v>851115</v>
       </c>
       <c r="C158" s="3" t="n">
-        <v>4536</v>
+        <v>3772</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="B159" s="3" t="n">
-        <v>1250968</v>
+        <v>608733</v>
       </c>
       <c r="C159" s="3" t="n">
-        <v>4433</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="B160" s="3" t="n">
-        <v>1248021</v>
+        <v>495210</v>
       </c>
       <c r="C160" s="3" t="n">
-        <v>4441</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="B161" s="3" t="n">
-        <v>998482</v>
+        <v>847706</v>
       </c>
       <c r="C161" s="3" t="n">
-        <v>2637</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="B162" s="3" t="n">
-        <v>734794</v>
+        <v>892186</v>
       </c>
       <c r="C162" s="3" t="n">
-        <v>2267</v>
+        <v>3988</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="B163" s="3" t="n">
-        <v>1230500</v>
+        <v>898663</v>
       </c>
       <c r="C163" s="3" t="n">
-        <v>4124</v>
+        <v>3855</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="B164" s="3" t="n">
-        <v>1244904</v>
+        <v>909030</v>
       </c>
       <c r="C164" s="3" t="n">
-        <v>4385</v>
+        <v>3958</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="B165" s="3" t="n">
-        <v>1284565</v>
+        <v>932060</v>
       </c>
       <c r="C165" s="3" t="n">
-        <v>4407</v>
+        <v>4370</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="B166" s="3" t="n">
-        <v>1295919</v>
+        <v>703656</v>
       </c>
       <c r="C166" s="3" t="n">
-        <v>4384</v>
+        <v>2638</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="B167" s="3" t="n">
-        <v>1286894</v>
+        <v>543914</v>
       </c>
       <c r="C167" s="3" t="n">
-        <v>4487</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="B168" s="3" t="n">
-        <v>923563</v>
+        <v>886745</v>
       </c>
       <c r="C168" s="3" t="n">
-        <v>2699</v>
+        <v>3864</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="B169" s="3" t="n">
-        <v>747602</v>
+        <v>902488</v>
       </c>
       <c r="C169" s="3" t="n">
-        <v>2347</v>
+        <v>3892</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="B170" s="3" t="n">
-        <v>1234690</v>
+        <v>905906</v>
       </c>
       <c r="C170" s="3" t="n">
-        <v>4376</v>
+        <v>4090</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="B171" s="3" t="n">
-        <v>1236846</v>
+        <v>897639</v>
       </c>
       <c r="C171" s="3" t="n">
-        <v>4323</v>
+        <v>3991</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="B172" s="3" t="n">
-        <v>1254695</v>
+        <v>864232</v>
       </c>
       <c r="C172" s="3" t="n">
-        <v>4392</v>
+        <v>3548</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="B173" s="3" t="n">
-        <v>1267352</v>
+        <v>629359</v>
       </c>
       <c r="C173" s="3" t="n">
-        <v>4646</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="B174" s="3" t="n">
-        <v>1235488</v>
+        <v>617875</v>
       </c>
       <c r="C174" s="3" t="n">
-        <v>4091</v>
+        <v>2733</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="B175" s="3" t="n">
-        <v>947186</v>
+        <v>913440</v>
       </c>
       <c r="C175" s="3" t="n">
-        <v>2554</v>
+        <v>3957</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="B176" s="3" t="n">
-        <v>768694</v>
+        <v>945518</v>
       </c>
       <c r="C176" s="3" t="n">
-        <v>2619</v>
+        <v>4279</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="B177" s="3" t="n">
-        <v>1201080</v>
+        <v>912103</v>
       </c>
       <c r="C177" s="3" t="n">
-        <v>3989</v>
+        <v>3652</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="B178" s="3" t="n">
-        <v>1227753</v>
+        <v>890290</v>
       </c>
       <c r="C178" s="3" t="n">
-        <v>4107</v>
+        <v>3545</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="B179" s="3" t="n">
-        <v>1249255</v>
+        <v>870761</v>
       </c>
       <c r="C179" s="3" t="n">
-        <v>4459</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="B180" s="3" t="n">
-        <v>1238903</v>
+        <v>633500</v>
       </c>
       <c r="C180" s="3" t="n">
-        <v>4430</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="B181" s="3" t="n">
-        <v>1225926</v>
+        <v>496299</v>
       </c>
       <c r="C181" s="3" t="n">
-        <v>4072</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B182" s="3" t="n">
-        <v>872072</v>
+        <v>837902</v>
       </c>
       <c r="C182" s="3" t="n">
-        <v>2226</v>
+        <v>3329</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B183" s="3" t="n">
-        <v>663601</v>
+        <v>863886</v>
       </c>
       <c r="C183" s="3" t="n">
-        <v>1992</v>
+        <v>3467</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="B184" s="3" t="n">
-        <v>1182600</v>
+        <v>864392</v>
       </c>
       <c r="C184" s="3" t="n">
-        <v>3801</v>
+        <v>3317</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="B185" s="3" t="n">
-        <v>1213861</v>
+        <v>872942</v>
       </c>
       <c r="C185" s="3" t="n">
-        <v>3961</v>
+        <v>3518</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="B186" s="3" t="n">
-        <v>1213703</v>
+        <v>831134</v>
       </c>
       <c r="C186" s="3" t="n">
-        <v>4152</v>
+        <v>3028</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="B187" s="3" t="n">
-        <v>1212854</v>
+        <v>575441</v>
       </c>
       <c r="C187" s="3" t="n">
-        <v>4168</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="B188" s="3" t="n">
-        <v>1211218</v>
+        <v>487199</v>
       </c>
       <c r="C188" s="3" t="n">
-        <v>4334</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="B189" s="3" t="n">
-        <v>965831</v>
+        <v>823863</v>
       </c>
       <c r="C189" s="3" t="n">
-        <v>3009</v>
+        <v>3251</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="B190" s="3" t="n">
-        <v>722395</v>
+        <v>851472</v>
       </c>
       <c r="C190" s="3" t="n">
-        <v>2354</v>
+        <v>3238</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="B191" s="3" t="n">
-        <v>1261710</v>
+        <v>860363</v>
       </c>
       <c r="C191" s="3" t="n">
-        <v>4822</v>
+        <v>3432</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="B192" s="3" t="n">
-        <v>1257023</v>
+        <v>853590</v>
       </c>
       <c r="C192" s="3" t="n">
-        <v>4419</v>
+        <v>3296</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="B193" s="3" t="n">
-        <v>1310748</v>
+        <v>845392</v>
       </c>
       <c r="C193" s="3" t="n">
-        <v>5763</v>
+        <v>3302</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="B194" s="3" t="n">
-        <v>1320599</v>
+        <v>612286</v>
       </c>
       <c r="C194" s="3" t="n">
-        <v>5317</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="B195" s="3" t="n">
-        <v>1321505</v>
+        <v>478464</v>
       </c>
       <c r="C195" s="3" t="n">
-        <v>5104</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="B196" s="3" t="n">
-        <v>986432</v>
+        <v>836722</v>
       </c>
       <c r="C196" s="3" t="n">
-        <v>2705</v>
+        <v>3406</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="B197" s="3" t="n">
-        <v>743602</v>
+        <v>860489</v>
       </c>
       <c r="C197" s="3" t="n">
-        <v>2309</v>
+        <v>3554</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="B198" s="3" t="n">
-        <v>1266008</v>
+        <v>844619</v>
       </c>
       <c r="C198" s="3" t="n">
-        <v>4509</v>
+        <v>3421</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="B199" s="3" t="n">
-        <v>1267815</v>
+        <v>836279</v>
       </c>
       <c r="C199" s="3" t="n">
-        <v>4527</v>
+        <v>3301</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="B200" s="3" t="n">
-        <v>1255257</v>
+        <v>832237</v>
       </c>
       <c r="C200" s="3" t="n">
-        <v>4303</v>
+        <v>3283</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="B201" s="3" t="n">
-        <v>1259098</v>
+        <v>591919</v>
       </c>
       <c r="C201" s="3" t="n">
-        <v>4537</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="B202" s="3" t="n">
-        <v>1025799</v>
+        <v>476490</v>
       </c>
       <c r="C202" s="3" t="n">
-        <v>3262</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="B203" s="3" t="n">
-        <v>829099</v>
+        <v>831114</v>
       </c>
       <c r="C203" s="3" t="n">
-        <v>2309</v>
+        <v>3350</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="B204" s="3" t="n">
-        <v>760663</v>
+        <v>868184</v>
       </c>
       <c r="C204" s="3" t="n">
-        <v>2373</v>
+        <v>3641</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="B205" s="3" t="n">
-        <v>1235126</v>
+        <v>871102</v>
       </c>
       <c r="C205" s="3" t="n">
-        <v>4103</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="B206" s="3" t="n">
-        <v>1276774</v>
+        <v>890843</v>
       </c>
       <c r="C206" s="3" t="n">
-        <v>4475</v>
+        <v>3819</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="B207" s="3" t="n">
-        <v>1290074</v>
+        <v>845526</v>
       </c>
       <c r="C207" s="3" t="n">
-        <v>4518</v>
+        <v>3394</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="B208" s="3" t="n">
-        <v>1289016</v>
+        <v>618687</v>
       </c>
       <c r="C208" s="3" t="n">
-        <v>4801</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="B209" s="3" t="n">
-        <v>1266258</v>
+        <v>503292</v>
       </c>
       <c r="C209" s="3" t="n">
-        <v>4397</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="B210" s="3" t="n">
-        <v>961133</v>
+        <v>855486</v>
       </c>
       <c r="C210" s="3" t="n">
-        <v>2555</v>
+        <v>3450</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="B211" s="3" t="n">
-        <v>744261</v>
+        <v>861464</v>
       </c>
       <c r="C211" s="3" t="n">
-        <v>2356</v>
+        <v>3421</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="B212" s="3" t="n">
-        <v>1216927</v>
+        <v>884152</v>
       </c>
       <c r="C212" s="3" t="n">
-        <v>4112</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="B213" s="3" t="n">
-        <v>1240069</v>
+        <v>890909</v>
       </c>
       <c r="C213" s="3" t="n">
-        <v>3928</v>
+        <v>3903</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B214" s="3" t="n">
-        <v>1257607</v>
+        <v>870937</v>
       </c>
       <c r="C214" s="3" t="n">
-        <v>4248</v>
+        <v>3663</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B215" s="3" t="n">
-        <v>1278013</v>
+        <v>647389</v>
       </c>
       <c r="C215" s="3" t="n">
-        <v>4585</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B216" s="3" t="n">
-        <v>1237187</v>
+        <v>496184</v>
       </c>
       <c r="C216" s="3" t="n">
-        <v>3918</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B217" s="3" t="n">
-        <v>834422</v>
+        <v>835752</v>
       </c>
       <c r="C217" s="3" t="n">
-        <v>1985</v>
+        <v>3383</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B218" s="3" t="n">
-        <v>651250</v>
+        <v>847853</v>
       </c>
       <c r="C218" s="3" t="n">
-        <v>1907</v>
+        <v>3419</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="n">
+        <v>850350</v>
+      </c>
+      <c r="C219" s="3" t="n">
+        <v>3283</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="n">
+        <v>849439</v>
+      </c>
+      <c r="C220" s="3" t="n">
+        <v>3424</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="n">
+        <v>823479</v>
+      </c>
+      <c r="C221" s="3" t="n">
+        <v>3249</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="n">
+        <v>596885</v>
+      </c>
+      <c r="C222" s="3" t="n">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="n">
+        <v>478916</v>
+      </c>
+      <c r="C223" s="3" t="n">
+        <v>2045</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="n">
+        <v>837782</v>
+      </c>
+      <c r="C224" s="3" t="n">
+        <v>3367</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="n">
+        <v>863340</v>
+      </c>
+      <c r="C225" s="3" t="n">
+        <v>3637</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="n">
+        <v>865620</v>
+      </c>
+      <c r="C226" s="3" t="n">
+        <v>3587</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="n">
+        <v>877329</v>
+      </c>
+      <c r="C227" s="3" t="n">
+        <v>3703</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="n">
+        <v>862107</v>
+      </c>
+      <c r="C228" s="3" t="n">
+        <v>3513</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="n">
+        <v>624259</v>
+      </c>
+      <c r="C229" s="3" t="n">
+        <v>2417</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="n">
+        <v>476547</v>
+      </c>
+      <c r="C230" s="3" t="n">
+        <v>2096</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="n">
+        <v>851521</v>
+      </c>
+      <c r="C231" s="3" t="n">
+        <v>3445</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="n">
+        <v>881467</v>
+      </c>
+      <c r="C232" s="3" t="n">
+        <v>3683</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="n">
+        <v>887553</v>
+      </c>
+      <c r="C233" s="3" t="n">
+        <v>3855</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="n">
+        <v>878944</v>
+      </c>
+      <c r="C234" s="3" t="n">
+        <v>3810</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="n">
+        <v>898361</v>
+      </c>
+      <c r="C235" s="3" t="n">
+        <v>4150</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="n">
+        <v>668290</v>
+      </c>
+      <c r="C236" s="3" t="n">
+        <v>2806</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="n">
+        <v>523310</v>
+      </c>
+      <c r="C237" s="3" t="n">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="n">
+        <v>898746</v>
+      </c>
+      <c r="C238" s="3" t="n">
+        <v>4197</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="n">
+        <v>917737</v>
+      </c>
+      <c r="C239" s="3" t="n">
+        <v>4197</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="n">
+        <v>914524</v>
+      </c>
+      <c r="C240" s="3" t="n">
+        <v>4297</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="n">
+        <v>923612</v>
+      </c>
+      <c r="C241" s="3" t="n">
+        <v>4250</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="n">
+        <v>897993</v>
+      </c>
+      <c r="C242" s="3" t="n">
+        <v>3966</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="n">
+        <v>638405</v>
+      </c>
+      <c r="C243" s="3" t="n">
+        <v>2592</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="n">
+        <v>536868</v>
+      </c>
+      <c r="C244" s="3" t="n">
+        <v>2649</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="n">
+        <v>888452</v>
+      </c>
+      <c r="C245" s="3" t="n">
+        <v>3921</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="n">
+        <v>927773</v>
+      </c>
+      <c r="C246" s="3" t="n">
+        <v>4355</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="n">
+        <v>910536</v>
+      </c>
+      <c r="C247" s="3" t="n">
+        <v>4290</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="n">
+        <v>920891</v>
+      </c>
+      <c r="C248" s="3" t="n">
+        <v>4371</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="n">
+        <v>900776</v>
+      </c>
+      <c r="C249" s="3" t="n">
+        <v>3996</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="n">
+        <v>674594</v>
+      </c>
+      <c r="C250" s="3" t="n">
+        <v>2688</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="n">
+        <v>529666</v>
+      </c>
+      <c r="C251" s="3" t="n">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="n">
+        <v>901207</v>
+      </c>
+      <c r="C252" s="3" t="n">
+        <v>3969</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="n">
+        <v>927193</v>
+      </c>
+      <c r="C253" s="3" t="n">
+        <v>4202</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="n">
+        <v>934459</v>
+      </c>
+      <c r="C254" s="3" t="n">
+        <v>4090</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="n">
+        <v>944093</v>
+      </c>
+      <c r="C255" s="3" t="n">
+        <v>4486</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="n">
+        <v>919046</v>
+      </c>
+      <c r="C256" s="3" t="n">
+        <v>4055</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="n">
+        <v>648964</v>
+      </c>
+      <c r="C257" s="3" t="n">
+        <v>2610</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="n">
+        <v>520527</v>
+      </c>
+      <c r="C258" s="3" t="n">
+        <v>2570</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="n">
+        <v>918582</v>
+      </c>
+      <c r="C259" s="3" t="n">
+        <v>4030</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="n">
+        <v>938998</v>
+      </c>
+      <c r="C260" s="3" t="n">
+        <v>4272</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="n">
+        <v>967975</v>
+      </c>
+      <c r="C261" s="3" t="n">
+        <v>4749</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="n">
+        <v>1024179</v>
+      </c>
+      <c r="C262" s="3" t="n">
+        <v>5637</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="n">
+        <v>918496</v>
+      </c>
+      <c r="C263" s="3" t="n">
+        <v>3970</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="n">
+        <v>632552</v>
+      </c>
+      <c r="C264" s="3" t="n">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="n">
+        <v>509597</v>
+      </c>
+      <c r="C265" s="3" t="n">
+        <v>2377</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="n">
+        <v>914607</v>
+      </c>
+      <c r="C266" s="3" t="n">
+        <v>4019</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="n">
+        <v>938182</v>
+      </c>
+      <c r="C267" s="3" t="n">
+        <v>4223</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="n">
+        <v>928479</v>
+      </c>
+      <c r="C268" s="3" t="n">
+        <v>4256</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="n">
+        <v>926854</v>
+      </c>
+      <c r="C269" s="3" t="n">
+        <v>4182</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="n">
+        <v>909661</v>
+      </c>
+      <c r="C270" s="3" t="n">
+        <v>3884</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="B271" s="3" t="n">
+        <v>627317</v>
+      </c>
+      <c r="C271" s="3" t="n">
+        <v>2459</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="n">
+        <v>569769</v>
+      </c>
+      <c r="C272" s="3" t="n">
+        <v>2382</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="n">
+        <v>864204</v>
+      </c>
+      <c r="C273" s="3" t="n">
+        <v>3588</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="n">
+        <v>878949</v>
+      </c>
+      <c r="C274" s="3" t="n">
+        <v>3493</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="n">
+        <v>653225</v>
+      </c>
+      <c r="C275" s="3" t="n">
+        <v>2518</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="n">
+        <v>667781</v>
+      </c>
+      <c r="C276" s="3" t="n">
+        <v>2725</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="B277" s="3" t="n">
+        <v>632253</v>
+      </c>
+      <c r="C277" s="3" t="n">
+        <v>2542</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="n">
+        <v>570260</v>
+      </c>
+      <c r="C278" s="3" t="n">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="B279" s="3" t="n">
+        <v>484894</v>
+      </c>
+      <c r="C279" s="3" t="n">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="B280" s="3" t="n">
+        <v>622794</v>
+      </c>
+      <c r="C280" s="3" t="n">
+        <v>2566</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="B281" s="3" t="n">
+        <v>663633</v>
+      </c>
+      <c r="C281" s="3" t="n">
+        <v>2726</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="B282" s="3" t="n">
+        <v>720231</v>
+      </c>
+      <c r="C282" s="3" t="n">
+        <v>3143</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="B283" s="3" t="n">
+        <v>941960</v>
+      </c>
+      <c r="C283" s="3" t="n">
+        <v>4168</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="B284" s="3" t="n">
+        <v>952142</v>
+      </c>
+      <c r="C284" s="3" t="n">
+        <v>4661</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="B285" s="3" t="n">
+        <v>866403</v>
+      </c>
+      <c r="C285" s="3" t="n">
+        <v>4285</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="B286" s="3" t="n">
+        <v>661836</v>
+      </c>
+      <c r="C286" s="3" t="n">
+        <v>3214</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="B287" s="3" t="n">
+        <v>1081909</v>
+      </c>
+      <c r="C287" s="3" t="n">
+        <v>5285</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="B288" s="3" t="n">
+        <v>1100392</v>
+      </c>
+      <c r="C288" s="3" t="n">
+        <v>5422</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="B289" s="3" t="n">
+        <v>1102014</v>
+      </c>
+      <c r="C289" s="3" t="n">
+        <v>4980</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="B290" s="3" t="n">
+        <v>1089127</v>
+      </c>
+      <c r="C290" s="3" t="n">
+        <v>4711</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="B291" s="3" t="n">
+        <v>1100875</v>
+      </c>
+      <c r="C291" s="3" t="n">
+        <v>5363</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="B292" s="3" t="n">
+        <v>848155</v>
+      </c>
+      <c r="C292" s="3" t="n">
+        <v>3244</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="B293" s="3" t="n">
+        <v>688822</v>
+      </c>
+      <c r="C293" s="3" t="n">
+        <v>2797</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="B294" s="3" t="n">
+        <v>1060774</v>
+      </c>
+      <c r="C294" s="3" t="n">
+        <v>4374</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="B295" s="3" t="n">
+        <v>1094995</v>
+      </c>
+      <c r="C295" s="3" t="n">
+        <v>4770</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="B296" s="3" t="n">
+        <v>1112008</v>
+      </c>
+      <c r="C296" s="3" t="n">
+        <v>4840</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="B297" s="3" t="n">
+        <v>1105935</v>
+      </c>
+      <c r="C297" s="3" t="n">
+        <v>4836</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="B298" s="3" t="n">
+        <v>1081041</v>
+      </c>
+      <c r="C298" s="3" t="n">
+        <v>4426</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="B299" s="3" t="n">
+        <v>808533</v>
+      </c>
+      <c r="C299" s="3" t="n">
+        <v>2668</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="B300" s="3" t="n">
+        <v>688233</v>
+      </c>
+      <c r="C300" s="3" t="n">
+        <v>2766</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="B301" s="3" t="n">
+        <v>1103886</v>
+      </c>
+      <c r="C301" s="3" t="n">
+        <v>4549</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="n">
+        <v>1114525</v>
+      </c>
+      <c r="C302" s="3" t="n">
+        <v>4813</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="B303" s="3" t="n">
+        <v>1112246</v>
+      </c>
+      <c r="C303" s="3" t="n">
+        <v>4860</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="B304" s="3" t="n">
+        <v>1155860</v>
+      </c>
+      <c r="C304" s="3" t="n">
+        <v>5797</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="B305" s="3" t="n">
+        <v>1089363</v>
+      </c>
+      <c r="C305" s="3" t="n">
+        <v>4396</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="B306" s="3" t="n">
+        <v>803129</v>
+      </c>
+      <c r="C306" s="3" t="n">
+        <v>2702</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="B307" s="3" t="n">
+        <v>644713</v>
+      </c>
+      <c r="C307" s="3" t="n">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="B308" s="3" t="n">
+        <v>1064840</v>
+      </c>
+      <c r="C308" s="3" t="n">
+        <v>4214</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="B309" s="3" t="n">
+        <v>1082312</v>
+      </c>
+      <c r="C309" s="3" t="n">
+        <v>4338</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="B310" s="3" t="n">
+        <v>1090187</v>
+      </c>
+      <c r="C310" s="3" t="n">
+        <v>4612</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="B311" s="3" t="n">
+        <v>1079802</v>
+      </c>
+      <c r="C311" s="3" t="n">
+        <v>4371</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="B312" s="3" t="n">
+        <v>1071894</v>
+      </c>
+      <c r="C312" s="3" t="n">
+        <v>4355</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="B313" s="3" t="n">
+        <v>782244</v>
+      </c>
+      <c r="C313" s="3" t="n">
+        <v>2668</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="B314" s="3" t="n">
+        <v>650187</v>
+      </c>
+      <c r="C314" s="3" t="n">
+        <v>2447</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="B315" s="3" t="n">
+        <v>1055984</v>
+      </c>
+      <c r="C315" s="3" t="n">
+        <v>4084</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="B316" s="3" t="n">
+        <v>1071106</v>
+      </c>
+      <c r="C316" s="3" t="n">
+        <v>4172</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="B317" s="3" t="n">
+        <v>1066873</v>
+      </c>
+      <c r="C317" s="3" t="n">
+        <v>4166</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="B318" s="3" t="n">
+        <v>1081003</v>
+      </c>
+      <c r="C318" s="3" t="n">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B319" s="3" t="n">
+        <v>1027351</v>
+      </c>
+      <c r="C319" s="3" t="n">
+        <v>4829</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B320" s="3" t="n">
+        <v>774430</v>
+      </c>
+      <c r="C320" s="3" t="n">
+        <v>2822</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="B321" s="3" t="n">
+        <v>604441</v>
+      </c>
+      <c r="C321" s="3" t="n">
+        <v>2487</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="B322" s="3" t="n">
+        <v>1007411</v>
+      </c>
+      <c r="C322" s="3" t="n">
+        <v>4338</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="B323" s="3" t="n">
+        <v>1036338</v>
+      </c>
+      <c r="C323" s="3" t="n">
+        <v>4509</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="B324" s="3" t="n">
+        <v>1032019</v>
+      </c>
+      <c r="C324" s="3" t="n">
+        <v>4503</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="B325" s="3" t="n">
+        <v>1032227</v>
+      </c>
+      <c r="C325" s="3" t="n">
+        <v>4805</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="B326" s="3" t="n">
+        <v>1059121</v>
+      </c>
+      <c r="C326" s="3" t="n">
+        <v>5147</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="B327" s="3" t="n">
+        <v>764400</v>
+      </c>
+      <c r="C327" s="3" t="n">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="B328" s="3" t="n">
+        <v>585242</v>
+      </c>
+      <c r="C328" s="3" t="n">
+        <v>2476</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="B329" s="3" t="n">
+        <v>1011935</v>
+      </c>
+      <c r="C329" s="3" t="n">
+        <v>4189</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="B330" s="3" t="n">
+        <v>1051744</v>
+      </c>
+      <c r="C330" s="3" t="n">
+        <v>4506</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="B331" s="3" t="n">
+        <v>1029347</v>
+      </c>
+      <c r="C331" s="3" t="n">
+        <v>4185</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="B332" s="3" t="n">
+        <v>1004148</v>
+      </c>
+      <c r="C332" s="3" t="n">
+        <v>3843</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="B333" s="3" t="n">
+        <v>979585</v>
+      </c>
+      <c r="C333" s="3" t="n">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="B334" s="3" t="n">
+        <v>736993</v>
+      </c>
+      <c r="C334" s="3" t="n">
+        <v>2576</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="B335" s="3" t="n">
+        <v>586155</v>
+      </c>
+      <c r="C335" s="3" t="n">
+        <v>2298</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="B336" s="3" t="n">
+        <v>990914</v>
+      </c>
+      <c r="C336" s="3" t="n">
+        <v>4054</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="B337" s="3" t="n">
+        <v>1012612</v>
+      </c>
+      <c r="C337" s="3" t="n">
+        <v>4254</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="B338" s="3" t="n">
+        <v>1010840</v>
+      </c>
+      <c r="C338" s="3" t="n">
+        <v>4373</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="B339" s="3" t="n">
+        <v>1006405</v>
+      </c>
+      <c r="C339" s="3" t="n">
+        <v>4042</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="B340" s="3" t="n">
+        <v>981577</v>
+      </c>
+      <c r="C340" s="3" t="n">
+        <v>3749</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="B341" s="3" t="n">
+        <v>723677</v>
+      </c>
+      <c r="C341" s="3" t="n">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="B342" s="3" t="n">
+        <v>560746</v>
+      </c>
+      <c r="C342" s="3" t="n">
+        <v>2252</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="B343" s="3" t="n">
+        <v>979486</v>
+      </c>
+      <c r="C343" s="3" t="n">
+        <v>3783</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="B344" s="3" t="n">
+        <v>1001761</v>
+      </c>
+      <c r="C344" s="3" t="n">
+        <v>4081</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="B345" s="3" t="n">
+        <v>1012719</v>
+      </c>
+      <c r="C345" s="3" t="n">
+        <v>4218</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="B346" s="3" t="n">
+        <v>1034741</v>
+      </c>
+      <c r="C346" s="3" t="n">
+        <v>4788</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="B347" s="3" t="n">
+        <v>994479</v>
+      </c>
+      <c r="C347" s="3" t="n">
+        <v>4177</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="B348" s="3" t="n">
+        <v>762590</v>
+      </c>
+      <c r="C348" s="3" t="n">
+        <v>2844</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-14</t>
+        </is>
+      </c>
+      <c r="B349" s="3" t="n">
+        <v>571768</v>
+      </c>
+      <c r="C349" s="3" t="n">
+        <v>2292</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="B350" s="3" t="n">
+        <v>971913</v>
+      </c>
+      <c r="C350" s="3" t="n">
+        <v>4154</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="B351" s="3" t="n">
+        <v>1020486</v>
+      </c>
+      <c r="C351" s="3" t="n">
+        <v>4667</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="B352" s="3" t="n">
+        <v>1013829</v>
+      </c>
+      <c r="C352" s="3" t="n">
+        <v>4344</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="B353" s="3" t="n">
+        <v>1018149</v>
+      </c>
+      <c r="C353" s="3" t="n">
+        <v>4680</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="B354" s="3" t="n">
+        <v>1000679</v>
+      </c>
+      <c r="C354" s="3" t="n">
+        <v>4295</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="B355" s="3" t="n">
+        <v>727651</v>
+      </c>
+      <c r="C355" s="3" t="n">
+        <v>2554</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="B356" s="3" t="n">
+        <v>550088</v>
+      </c>
+      <c r="C356" s="3" t="n">
+        <v>2352</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="B357" s="3" t="n">
+        <v>974857</v>
+      </c>
+      <c r="C357" s="3" t="n">
+        <v>4273</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="B358" s="3" t="n">
+        <v>1016848</v>
+      </c>
+      <c r="C358" s="3" t="n">
+        <v>4640</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="B359" s="3" t="n">
+        <v>1012670</v>
+      </c>
+      <c r="C359" s="3" t="n">
+        <v>4760</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="B360" s="3" t="n">
+        <v>987369</v>
+      </c>
+      <c r="C360" s="3" t="n">
+        <v>4259</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="B361" s="3" t="n">
+        <v>975070</v>
+      </c>
+      <c r="C361" s="3" t="n">
+        <v>4513</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="B362" s="3" t="n">
+        <v>736971</v>
+      </c>
+      <c r="C362" s="3" t="n">
+        <v>3320</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="B363" s="3" t="n">
+        <v>582533</v>
+      </c>
+      <c r="C363" s="3" t="n">
+        <v>2933</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="B364" s="3" t="n">
+        <v>1022159</v>
+      </c>
+      <c r="C364" s="3" t="n">
+        <v>5602</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="B365" s="3" t="n">
+        <v>1032078</v>
+      </c>
+      <c r="C365" s="3" t="n">
+        <v>5284</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="B366" s="3" t="n">
+        <v>984399</v>
+      </c>
+      <c r="C366" s="3" t="n">
+        <v>4537</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B367" s="3" t="n">
+        <v>697434</v>
+      </c>
+      <c r="C367" s="3" t="n">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B368" s="3" t="n">
+        <v>738751</v>
+      </c>
+      <c r="C368" s="3" t="n">
+        <v>3367</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="B369" s="3" t="n">
+        <v>763515</v>
+      </c>
+      <c r="C369" s="3" t="n">
+        <v>3456</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B370" s="3" t="n">
+        <v>777600</v>
+      </c>
+      <c r="C370" s="3" t="n">
+        <v>3539</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="B371" s="3" t="n">
+        <v>1050682</v>
+      </c>
+      <c r="C371" s="3" t="n">
+        <v>4920</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B372" s="3" t="n">
+        <v>1064749</v>
+      </c>
+      <c r="C372" s="3" t="n">
+        <v>5003</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B373" s="3" t="n">
+        <v>1064528</v>
+      </c>
+      <c r="C373" s="3" t="n">
+        <v>5242</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="B374" s="3" t="n">
+        <v>1055436</v>
+      </c>
+      <c r="C374" s="3" t="n">
+        <v>5216</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B375" s="3" t="n">
+        <v>1049381</v>
+      </c>
+      <c r="C375" s="3" t="n">
+        <v>5024</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B376" s="3" t="n">
+        <v>783241</v>
+      </c>
+      <c r="C376" s="3" t="n">
+        <v>3538</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="B377" s="3" t="n">
+        <v>618151</v>
+      </c>
+      <c r="C377" s="3" t="n">
+        <v>3065</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B378" s="3" t="n">
+        <v>1077513</v>
+      </c>
+      <c r="C378" s="3" t="n">
+        <v>5282</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B379" s="3" t="n">
+        <v>1107598</v>
+      </c>
+      <c r="C379" s="3" t="n">
+        <v>5708</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="B380" s="3" t="n">
+        <v>1116877</v>
+      </c>
+      <c r="C380" s="3" t="n">
+        <v>5823</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="B381" s="3" t="n">
+        <v>1117369</v>
+      </c>
+      <c r="C381" s="3" t="n">
+        <v>5957</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B382" s="3" t="n">
+        <v>1061788</v>
+      </c>
+      <c r="C382" s="3" t="n">
+        <v>5184</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="B383" s="3" t="n">
+        <v>782239</v>
+      </c>
+      <c r="C383" s="3" t="n">
+        <v>3332</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="B384" s="3" t="n">
+        <v>639477</v>
+      </c>
+      <c r="C384" s="3" t="n">
+        <v>3088</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B385" s="3" t="n">
+        <v>1039566</v>
+      </c>
+      <c r="C385" s="3" t="n">
+        <v>4897</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B386" s="3" t="n">
+        <v>1080996</v>
+      </c>
+      <c r="C386" s="3" t="n">
+        <v>5209</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B387" s="3" t="n">
+        <v>1097765</v>
+      </c>
+      <c r="C387" s="3" t="n">
+        <v>5843</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B388" s="3" t="n">
+        <v>1090907</v>
+      </c>
+      <c r="C388" s="3" t="n">
+        <v>5831</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="B389" s="3" t="n">
+        <v>1081513</v>
+      </c>
+      <c r="C389" s="3" t="n">
+        <v>5975</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="B390" s="3" t="n">
+        <v>819534</v>
+      </c>
+      <c r="C390" s="3" t="n">
+        <v>4080</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B391" s="3" t="n">
+        <v>648203</v>
+      </c>
+      <c r="C391" s="3" t="n">
+        <v>3577</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B392" s="3" t="n">
+        <v>1089991</v>
+      </c>
+      <c r="C392" s="3" t="n">
+        <v>6180</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B393" s="3" t="n">
+        <v>1110726</v>
+      </c>
+      <c r="C393" s="3" t="n">
+        <v>6919</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B394" s="3" t="n">
+        <v>1160277</v>
+      </c>
+      <c r="C394" s="3" t="n">
+        <v>7889</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="B395" s="3" t="n">
+        <v>1228498</v>
+      </c>
+      <c r="C395" s="3" t="n">
+        <v>10498</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B396" s="3" t="n">
+        <v>1262245</v>
+      </c>
+      <c r="C396" s="3" t="n">
+        <v>12674</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B397" s="3" t="n">
+        <v>1061808</v>
+      </c>
+      <c r="C397" s="3" t="n">
+        <v>9406</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B398" s="3" t="n">
+        <v>834449</v>
+      </c>
+      <c r="C398" s="3" t="n">
+        <v>6280</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B399" s="3" t="n">
+        <v>1317266</v>
+      </c>
+      <c r="C399" s="3" t="n">
+        <v>12382</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B400" s="3" t="n">
+        <v>1276626</v>
+      </c>
+      <c r="C400" s="3" t="n">
+        <v>9864</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B401" s="3" t="n">
+        <v>1268744</v>
+      </c>
+      <c r="C401" s="3" t="n">
+        <v>9345</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B402" s="3" t="n">
+        <v>1262299</v>
+      </c>
+      <c r="C402" s="3" t="n">
+        <v>9713</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B403" s="3" t="n">
+        <v>1228655</v>
+      </c>
+      <c r="C403" s="3" t="n">
+        <v>8675</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B404" s="3" t="n">
+        <v>959856</v>
+      </c>
+      <c r="C404" s="3" t="n">
+        <v>4773</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B405" s="3" t="n">
+        <v>704573</v>
+      </c>
+      <c r="C405" s="3" t="n">
+        <v>3529</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B406" s="3" t="n">
+        <v>1148995</v>
+      </c>
+      <c r="C406" s="3" t="n">
+        <v>6321</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B407" s="3" t="n">
+        <v>1148909</v>
+      </c>
+      <c r="C407" s="3" t="n">
+        <v>6006</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B408" s="3" t="n">
+        <v>1136855</v>
+      </c>
+      <c r="C408" s="3" t="n">
+        <v>5870</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B409" s="3" t="n">
+        <v>1108698</v>
+      </c>
+      <c r="C409" s="3" t="n">
+        <v>5171</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B410" s="3" t="n">
+        <v>1087050</v>
+      </c>
+      <c r="C410" s="3" t="n">
+        <v>5478</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B411" s="3" t="n">
+        <v>836545</v>
+      </c>
+      <c r="C411" s="3" t="n">
+        <v>3099</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B412" s="3" t="n">
+        <v>628715</v>
+      </c>
+      <c r="C412" s="3" t="n">
+        <v>2317</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B413" s="3" t="n">
+        <v>739366</v>
+      </c>
+      <c r="C413" s="3" t="n">
+        <v>2711</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B414" s="3" t="n">
+        <v>785085</v>
+      </c>
+      <c r="C414" s="3" t="n">
+        <v>3106</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B415" s="3" t="n">
+        <v>785266</v>
+      </c>
+      <c r="C415" s="3" t="n">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B416" s="3" t="n">
+        <v>781480</v>
+      </c>
+      <c r="C416" s="3" t="n">
+        <v>3235</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B417" s="3" t="n">
+        <v>804540</v>
+      </c>
+      <c r="C417" s="3" t="n">
+        <v>3451</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B418" s="3" t="n">
+        <v>790059</v>
+      </c>
+      <c r="C418" s="3" t="n">
+        <v>3086</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B419" s="3" t="n">
+        <v>640467</v>
+      </c>
+      <c r="C419" s="3" t="n">
+        <v>2391</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B420" s="3" t="n">
+        <v>903843</v>
+      </c>
+      <c r="C420" s="3" t="n">
+        <v>4369</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B421" s="3" t="n">
+        <v>1162268</v>
+      </c>
+      <c r="C421" s="3" t="n">
+        <v>5748</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B422" s="3" t="n">
+        <v>1167330</v>
+      </c>
+      <c r="C422" s="3" t="n">
+        <v>5453</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B423" s="3" t="n">
+        <v>1174942</v>
+      </c>
+      <c r="C423" s="3" t="n">
+        <v>5961</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B424" s="3" t="n">
+        <v>1183555</v>
+      </c>
+      <c r="C424" s="3" t="n">
+        <v>5895</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B425" s="3" t="n">
+        <v>1161031</v>
+      </c>
+      <c r="C425" s="3" t="n">
+        <v>6225</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B426" s="3" t="n">
+        <v>1013315</v>
+      </c>
+      <c r="C426" s="3" t="n">
+        <v>5611</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B427" s="3" t="n">
+        <v>1347844</v>
+      </c>
+      <c r="C427" s="3" t="n">
+        <v>8387</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B428" s="3" t="n">
+        <v>1351006</v>
+      </c>
+      <c r="C428" s="3" t="n">
+        <v>8262</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B429" s="3" t="n">
+        <v>1341788</v>
+      </c>
+      <c r="C429" s="3" t="n">
+        <v>8010</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B430" s="3" t="n">
+        <v>1299978</v>
+      </c>
+      <c r="C430" s="3" t="n">
+        <v>7139</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B431" s="3" t="n">
+        <v>1274324</v>
+      </c>
+      <c r="C431" s="3" t="n">
+        <v>6838</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B432" s="3" t="n">
+        <v>1004620</v>
+      </c>
+      <c r="C432" s="3" t="n">
+        <v>4472</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B433" s="3" t="n">
+        <v>783047</v>
+      </c>
+      <c r="C433" s="3" t="n">
+        <v>3627</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B434" s="3" t="n">
+        <v>1287956</v>
+      </c>
+      <c r="C434" s="3" t="n">
+        <v>7218</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B435" s="3" t="n">
+        <v>1294487</v>
+      </c>
+      <c r="C435" s="3" t="n">
+        <v>6945</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B436" s="3" t="n">
+        <v>1288497</v>
+      </c>
+      <c r="C436" s="3" t="n">
+        <v>6632</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B437" s="3" t="n">
+        <v>1285044</v>
+      </c>
+      <c r="C437" s="3" t="n">
+        <v>6279</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B438" s="3" t="n">
+        <v>1268924</v>
+      </c>
+      <c r="C438" s="3" t="n">
+        <v>6259</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B439" s="3" t="n">
+        <v>982524</v>
+      </c>
+      <c r="C439" s="3" t="n">
+        <v>4376</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B440" s="3" t="n">
+        <v>801533</v>
+      </c>
+      <c r="C440" s="3" t="n">
+        <v>3737</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B441" s="3" t="n">
+        <v>1267504</v>
+      </c>
+      <c r="C441" s="3" t="n">
+        <v>6293</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B442" s="3" t="n">
+        <v>1270361</v>
+      </c>
+      <c r="C442" s="3" t="n">
+        <v>5864</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B443" s="3" t="n">
+        <v>1286717</v>
+      </c>
+      <c r="C443" s="3" t="n">
+        <v>6561</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B444" s="3" t="n">
+        <v>1347459</v>
+      </c>
+      <c r="C444" s="3" t="n">
+        <v>8092</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B445" s="3" t="n">
+        <v>1305185</v>
+      </c>
+      <c r="C445" s="3" t="n">
+        <v>6796</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B446" s="3" t="n">
+        <v>1005247</v>
+      </c>
+      <c r="C446" s="3" t="n">
+        <v>4688</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B447" s="3" t="n">
+        <v>842322</v>
+      </c>
+      <c r="C447" s="3" t="n">
+        <v>4072</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B448" s="3" t="n">
+        <v>1431359</v>
+      </c>
+      <c r="C448" s="3" t="n">
+        <v>9629</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B449" s="3" t="n">
+        <v>1402543</v>
+      </c>
+      <c r="C449" s="3" t="n">
+        <v>7913</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B450" s="3" t="n">
+        <v>1362207</v>
+      </c>
+      <c r="C450" s="3" t="n">
+        <v>6915</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B451" s="3" t="n">
+        <v>1337357</v>
+      </c>
+      <c r="C451" s="3" t="n">
+        <v>6432</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B452" s="3" t="n">
+        <v>1323689</v>
+      </c>
+      <c r="C452" s="3" t="n">
+        <v>6018</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B453" s="3" t="n">
+        <v>1024829</v>
+      </c>
+      <c r="C453" s="3" t="n">
+        <v>4035</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B454" s="3" t="n">
+        <v>810717</v>
+      </c>
+      <c r="C454" s="3" t="n">
+        <v>3380</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B455" s="3" t="n">
+        <v>1294899</v>
+      </c>
+      <c r="C455" s="3" t="n">
+        <v>5926</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B456" s="3" t="n">
+        <v>1305405</v>
+      </c>
+      <c r="C456" s="3" t="n">
+        <v>5518</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B457" s="3" t="n">
+        <v>1324127</v>
+      </c>
+      <c r="C457" s="3" t="n">
+        <v>5994</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B458" s="3" t="n">
+        <v>1331661</v>
+      </c>
+      <c r="C458" s="3" t="n">
+        <v>6306</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B459" s="3" t="n">
+        <v>1266079</v>
+      </c>
+      <c r="C459" s="3" t="n">
+        <v>4905</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B460" s="3" t="n">
+        <v>857954</v>
+      </c>
+      <c r="C460" s="3" t="n">
+        <v>2961</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B461" s="3" t="n">
+        <v>747474</v>
+      </c>
+      <c r="C461" s="3" t="n">
+        <v>2839</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B462" s="3" t="n">
+        <v>1015920</v>
+      </c>
+      <c r="C462" s="3" t="n">
+        <v>4259</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B463" s="3" t="n">
+        <v>1306284</v>
+      </c>
+      <c r="C463" s="3" t="n">
+        <v>5524</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B464" s="3" t="n">
+        <v>1409776</v>
+      </c>
+      <c r="C464" s="3" t="n">
+        <v>6730</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B465" s="3" t="n">
+        <v>1352125</v>
+      </c>
+      <c r="C465" s="3" t="n">
+        <v>5922</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B466" s="3" t="n">
+        <v>1297181</v>
+      </c>
+      <c r="C466" s="3" t="n">
+        <v>5038</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B467" s="3" t="n">
+        <v>987708</v>
+      </c>
+      <c r="C467" s="3" t="n">
+        <v>3490</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B468" s="3" t="n">
+        <v>905167</v>
+      </c>
+      <c r="C468" s="3" t="n">
+        <v>3873</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B469" s="3" t="n">
+        <v>1311431</v>
+      </c>
+      <c r="C469" s="3" t="n">
+        <v>5479</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B470" s="3" t="n">
+        <v>1295368</v>
+      </c>
+      <c r="C470" s="3" t="n">
+        <v>5018</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B471" s="3" t="n">
+        <v>1292279</v>
+      </c>
+      <c r="C471" s="3" t="n">
+        <v>4893</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B472" s="3" t="n">
+        <v>1280175</v>
+      </c>
+      <c r="C472" s="3" t="n">
+        <v>4656</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B473" s="3" t="n">
+        <v>1284058</v>
+      </c>
+      <c r="C473" s="3" t="n">
+        <v>4877</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B474" s="3" t="n">
+        <v>1039217</v>
+      </c>
+      <c r="C474" s="3" t="n">
+        <v>3582</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B475" s="3" t="n">
+        <v>817110</v>
+      </c>
+      <c r="C475" s="3" t="n">
+        <v>3125</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B476" s="3" t="n">
+        <v>1272666</v>
+      </c>
+      <c r="C476" s="3" t="n">
+        <v>4847</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B477" s="3" t="n">
+        <v>1284351</v>
+      </c>
+      <c r="C477" s="3" t="n">
+        <v>4901</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B478" s="3" t="n">
+        <v>1270675</v>
+      </c>
+      <c r="C478" s="3" t="n">
+        <v>4877</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B479" s="3" t="n">
+        <v>1267728</v>
+      </c>
+      <c r="C479" s="3" t="n">
+        <v>5031</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B480" s="3" t="n">
+        <v>1263222</v>
+      </c>
+      <c r="C480" s="3" t="n">
+        <v>5043</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B481" s="3" t="n">
+        <v>916309</v>
+      </c>
+      <c r="C481" s="3" t="n">
+        <v>2871</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B482" s="3" t="n">
+        <v>768172</v>
+      </c>
+      <c r="C482" s="3" t="n">
+        <v>2690</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B483" s="3" t="n">
+        <v>1208252</v>
+      </c>
+      <c r="C483" s="3" t="n">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B484" s="3" t="n">
+        <v>1240181</v>
+      </c>
+      <c r="C484" s="3" t="n">
+        <v>4630</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B485" s="3" t="n">
+        <v>1234415</v>
+      </c>
+      <c r="C485" s="3" t="n">
+        <v>4429</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B486" s="3" t="n">
+        <v>1202546</v>
+      </c>
+      <c r="C486" s="3" t="n">
+        <v>4155</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B487" s="3" t="n">
+        <v>906841</v>
+      </c>
+      <c r="C487" s="3" t="n">
+        <v>2796</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B488" s="3" t="n">
+        <v>815379</v>
+      </c>
+      <c r="C488" s="3" t="n">
+        <v>2263</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B489" s="3" t="n">
+        <v>670309</v>
+      </c>
+      <c r="C489" s="3" t="n">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B490" s="3" t="n">
+        <v>900993</v>
+      </c>
+      <c r="C490" s="3" t="n">
+        <v>2981</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B491" s="3" t="n">
+        <v>998869</v>
+      </c>
+      <c r="C491" s="3" t="n">
+        <v>3227</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B492" s="3" t="n">
+        <v>1256736</v>
+      </c>
+      <c r="C492" s="3" t="n">
+        <v>4536</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B493" s="3" t="n">
+        <v>1250968</v>
+      </c>
+      <c r="C493" s="3" t="n">
+        <v>4433</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B494" s="3" t="n">
+        <v>1248021</v>
+      </c>
+      <c r="C494" s="3" t="n">
+        <v>4441</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B495" s="3" t="n">
+        <v>998482</v>
+      </c>
+      <c r="C495" s="3" t="n">
+        <v>2637</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B496" s="3" t="n">
+        <v>734794</v>
+      </c>
+      <c r="C496" s="3" t="n">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B497" s="3" t="n">
+        <v>1230500</v>
+      </c>
+      <c r="C497" s="3" t="n">
+        <v>4124</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B498" s="3" t="n">
+        <v>1244904</v>
+      </c>
+      <c r="C498" s="3" t="n">
+        <v>4385</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B499" s="3" t="n">
+        <v>1284565</v>
+      </c>
+      <c r="C499" s="3" t="n">
+        <v>4407</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B500" s="3" t="n">
+        <v>1295919</v>
+      </c>
+      <c r="C500" s="3" t="n">
+        <v>4384</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B501" s="3" t="n">
+        <v>1286894</v>
+      </c>
+      <c r="C501" s="3" t="n">
+        <v>4487</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B502" s="3" t="n">
+        <v>923563</v>
+      </c>
+      <c r="C502" s="3" t="n">
+        <v>2699</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B503" s="3" t="n">
+        <v>747602</v>
+      </c>
+      <c r="C503" s="3" t="n">
+        <v>2347</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B504" s="3" t="n">
+        <v>1234690</v>
+      </c>
+      <c r="C504" s="3" t="n">
+        <v>4376</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B505" s="3" t="n">
+        <v>1236846</v>
+      </c>
+      <c r="C505" s="3" t="n">
+        <v>4323</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B506" s="3" t="n">
+        <v>1254695</v>
+      </c>
+      <c r="C506" s="3" t="n">
+        <v>4392</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B507" s="3" t="n">
+        <v>1267352</v>
+      </c>
+      <c r="C507" s="3" t="n">
+        <v>4646</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B508" s="3" t="n">
+        <v>1235488</v>
+      </c>
+      <c r="C508" s="3" t="n">
+        <v>4091</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B509" s="3" t="n">
+        <v>947186</v>
+      </c>
+      <c r="C509" s="3" t="n">
+        <v>2554</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B510" s="3" t="n">
+        <v>768694</v>
+      </c>
+      <c r="C510" s="3" t="n">
+        <v>2619</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B511" s="3" t="n">
+        <v>1201080</v>
+      </c>
+      <c r="C511" s="3" t="n">
+        <v>3989</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B512" s="3" t="n">
+        <v>1227753</v>
+      </c>
+      <c r="C512" s="3" t="n">
+        <v>4107</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B513" s="3" t="n">
+        <v>1249255</v>
+      </c>
+      <c r="C513" s="3" t="n">
+        <v>4459</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B514" s="3" t="n">
+        <v>1238903</v>
+      </c>
+      <c r="C514" s="3" t="n">
+        <v>4430</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B515" s="3" t="n">
+        <v>1225926</v>
+      </c>
+      <c r="C515" s="3" t="n">
+        <v>4072</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B516" s="3" t="n">
+        <v>872072</v>
+      </c>
+      <c r="C516" s="3" t="n">
+        <v>2226</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B517" s="3" t="n">
+        <v>663601</v>
+      </c>
+      <c r="C517" s="3" t="n">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B518" s="3" t="n">
+        <v>1182600</v>
+      </c>
+      <c r="C518" s="3" t="n">
+        <v>3801</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B519" s="3" t="n">
+        <v>1213861</v>
+      </c>
+      <c r="C519" s="3" t="n">
+        <v>3961</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B520" s="3" t="n">
+        <v>1213703</v>
+      </c>
+      <c r="C520" s="3" t="n">
+        <v>4152</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B521" s="3" t="n">
+        <v>1212854</v>
+      </c>
+      <c r="C521" s="3" t="n">
+        <v>4168</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B522" s="3" t="n">
+        <v>1211218</v>
+      </c>
+      <c r="C522" s="3" t="n">
+        <v>4334</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B523" s="3" t="n">
+        <v>965831</v>
+      </c>
+      <c r="C523" s="3" t="n">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B524" s="3" t="n">
+        <v>722395</v>
+      </c>
+      <c r="C524" s="3" t="n">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B525" s="3" t="n">
+        <v>1261710</v>
+      </c>
+      <c r="C525" s="3" t="n">
+        <v>4822</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B526" s="3" t="n">
+        <v>1257023</v>
+      </c>
+      <c r="C526" s="3" t="n">
+        <v>4419</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B527" s="3" t="n">
+        <v>1310748</v>
+      </c>
+      <c r="C527" s="3" t="n">
+        <v>5763</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B528" s="3" t="n">
+        <v>1320599</v>
+      </c>
+      <c r="C528" s="3" t="n">
+        <v>5317</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B529" s="3" t="n">
+        <v>1321505</v>
+      </c>
+      <c r="C529" s="3" t="n">
+        <v>5104</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B530" s="3" t="n">
+        <v>986432</v>
+      </c>
+      <c r="C530" s="3" t="n">
+        <v>2705</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B531" s="3" t="n">
+        <v>743602</v>
+      </c>
+      <c r="C531" s="3" t="n">
+        <v>2309</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B532" s="3" t="n">
+        <v>1266008</v>
+      </c>
+      <c r="C532" s="3" t="n">
+        <v>4509</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B533" s="3" t="n">
+        <v>1267815</v>
+      </c>
+      <c r="C533" s="3" t="n">
+        <v>4527</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B534" s="3" t="n">
+        <v>1255257</v>
+      </c>
+      <c r="C534" s="3" t="n">
+        <v>4303</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B535" s="3" t="n">
+        <v>1259098</v>
+      </c>
+      <c r="C535" s="3" t="n">
+        <v>4537</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B536" s="3" t="n">
+        <v>1025799</v>
+      </c>
+      <c r="C536" s="3" t="n">
+        <v>3262</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B537" s="3" t="n">
+        <v>829099</v>
+      </c>
+      <c r="C537" s="3" t="n">
+        <v>2309</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B538" s="3" t="n">
+        <v>760663</v>
+      </c>
+      <c r="C538" s="3" t="n">
+        <v>2373</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B539" s="3" t="n">
+        <v>1235126</v>
+      </c>
+      <c r="C539" s="3" t="n">
+        <v>4103</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B540" s="3" t="n">
+        <v>1276774</v>
+      </c>
+      <c r="C540" s="3" t="n">
+        <v>4475</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B541" s="3" t="n">
+        <v>1290074</v>
+      </c>
+      <c r="C541" s="3" t="n">
+        <v>4518</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B542" s="3" t="n">
+        <v>1289016</v>
+      </c>
+      <c r="C542" s="3" t="n">
+        <v>4801</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B543" s="3" t="n">
+        <v>1266258</v>
+      </c>
+      <c r="C543" s="3" t="n">
+        <v>4397</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B544" s="3" t="n">
+        <v>961133</v>
+      </c>
+      <c r="C544" s="3" t="n">
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B545" s="3" t="n">
+        <v>744261</v>
+      </c>
+      <c r="C545" s="3" t="n">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B546" s="3" t="n">
+        <v>1216927</v>
+      </c>
+      <c r="C546" s="3" t="n">
+        <v>4112</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B547" s="3" t="n">
+        <v>1240069</v>
+      </c>
+      <c r="C547" s="3" t="n">
+        <v>3928</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B548" s="3" t="n">
+        <v>1257607</v>
+      </c>
+      <c r="C548" s="3" t="n">
+        <v>4248</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B549" s="3" t="n">
+        <v>1278013</v>
+      </c>
+      <c r="C549" s="3" t="n">
+        <v>4585</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B550" s="3" t="n">
+        <v>1237187</v>
+      </c>
+      <c r="C550" s="3" t="n">
+        <v>3918</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B551" s="3" t="n">
+        <v>834422</v>
+      </c>
+      <c r="C551" s="3" t="n">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B552" s="3" t="n">
+        <v>651250</v>
+      </c>
+      <c r="C552" s="3" t="n">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="2" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B219" s="3" t="n">
+      <c r="B553" s="3" t="n">
         <v>1196419</v>
       </c>
-      <c r="C219" s="3" t="n">
+      <c r="C553" s="3" t="n">
         <v>3777</v>
       </c>
     </row>
@@ -3309,7 +7651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3337,404 +7679,1015 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>251201~1207</t>
+          <t>250101~0107</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>898110</v>
+        <v>665324</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3611</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>251208~1214</t>
+          <t>250108~0114</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>908221</v>
+        <v>691625</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3740</v>
+        <v>2805</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>251215~1221</t>
+          <t>250115~0121</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>900399</v>
+        <v>701107</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3864</v>
+        <v>2777</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>251222~1228</t>
+          <t>250122~0128</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>898045</v>
+        <v>653513</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4100</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>251229~0104</t>
+          <t>250129~0204</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>859419</v>
+        <v>558005</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4065</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>260105~0111</t>
+          <t>250205~0211</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>955167</v>
+        <v>738733</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>4573</v>
+        <v>2944</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>260112~0118</t>
+          <t>250212~0218</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>986123</v>
+        <v>744021</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>4911</v>
+        <v>3018</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>260119~0125</t>
+          <t>250219~0225</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>979783</v>
+        <v>756004</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>5059</v>
+        <v>3117</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>260126~0201</t>
+          <t>250226~0304</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1106856</v>
+        <v>770955</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>8549</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>260202~0208</t>
+          <t>250305~0311</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1145431</v>
+        <v>770056</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>8326</v>
+        <v>3326</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>260209~0215</t>
+          <t>250312~0318</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1013681</v>
+        <v>783120</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>4895</v>
+        <v>3254</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>260216~0222</t>
+          <t>250319~0325</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>760895</v>
+        <v>753823</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>3013</v>
+        <v>3121</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>260223~0301</t>
+          <t>250326~0401</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1109469</v>
+        <v>744409</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>5609</v>
+        <v>3094</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>260302~0308</t>
+          <t>250402~0408</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>1200372</v>
+        <v>853540</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>6676</v>
+        <v>4736</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>260309~0315</t>
+          <t>250409~0415</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1172709</v>
+        <v>945151</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>5921</v>
+        <v>5215</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>260316~0322</t>
+          <t>250416~0422</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1189256</v>
+        <v>847408</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>6052</v>
+        <v>3724</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>260323~0329</t>
+          <t>250423~0429</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>1241814</v>
+        <v>851439</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>6332</v>
+        <v>3747</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>260330~0405</t>
+          <t>250430~0506</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>1161086</v>
+        <v>725249</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>4921</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>260406~0412</t>
+          <t>250507~0513</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1182023</v>
+        <v>848080</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>4977</v>
+        <v>3729</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>260413~0419</t>
+          <t>250514~0520</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1188520</v>
+        <v>803579</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>4519</v>
+        <v>3358</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>260420~0426</t>
+          <t>250521~0527</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>1149018</v>
+        <v>775171</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>4323</v>
+        <v>3211</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>260427~0503</t>
+          <t>250528~0603</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1039703</v>
+        <v>741010</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>3545</v>
+        <v>3096</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>260504~0510</t>
+          <t>250604~0610</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>1055552</v>
+        <v>774081</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>3503</v>
+        <v>3264</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>260511~0517</t>
+          <t>250611~0617</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1144850</v>
+        <v>825222</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>3833</v>
+        <v>3572</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>260518~0524</t>
+          <t>250618~0624</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>1134993</v>
+        <v>824853</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>3857</v>
+        <v>3534</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>260525~0531</t>
+          <t>250625~0701</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>1096941</v>
+        <v>786392</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3611</v>
+        <v>3065</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>260601~0607</t>
+          <t>250702~0708</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>1103209</v>
+        <v>758063</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>3683</v>
+        <v>2889</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>260608~0614</t>
+          <t>250709~0715</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1171660</v>
+        <v>763901</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>4348</v>
+        <v>3004</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>260615~0621</t>
+          <t>250716~0722</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>1094820</v>
+        <v>754406</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>3689</v>
+        <v>2979</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>260622~0628</t>
+          <t>250723~0729</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>1151806</v>
+        <v>778057</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>3886</v>
+        <v>3149</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>260629~0705</t>
+          <t>250730~0805</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>1102211</v>
+        <v>781882</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>3526</v>
+        <v>3220</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>250806~0812</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>757170</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>3017</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>250813~0819</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>776979</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>3206</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>250820~0826</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>810420</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>3641</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>250827~0902</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>818232</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>3719</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>250903~0909</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>823552</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>3716</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>250910~0916</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>832096</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>3730</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>250917~0923</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>843655</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>3912</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>250924~0930</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>815033</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>3463</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>251001~1007</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>613549</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>2436</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>251008~1014</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>903553</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>4311</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>251015~1021</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>997823</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>4320</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>251022~1028</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>1002023</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>4128</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>251029~1104</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>993209</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>251105~1111</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>971629</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>3816</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>251112~1118</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>942550</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>3960</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>251119~1125</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>933813</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>4061</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>251126~1202</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>905679</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>3562</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>251203~1209</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>894927</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>3547</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>251210~1216</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>909814</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>3877</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>251217~1223</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>900300</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>3877</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>251224~1230</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>906979</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>4382</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>251231~0106</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>868161</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>3928</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>260107~0113</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>965121</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>4725</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>260114~0120</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>976902</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>4784</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>260121~0127</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>991234</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>5486</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>260128~0203</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>1163024</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>9856</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>260204~0210</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>1103147</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>6909</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>260211~0217</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>903188</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>3965</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>260218~0224</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>838275</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>3627</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>260225~0303</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>1199860</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>6542</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>260304~0310</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>1183743</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>6321</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>260311~0317</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>1166341</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>5634</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>260318~0324</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>1231547</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>6822</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>260325~0331</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>1208443</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>5461</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>260401~0407</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>1121357</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>4684</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>260408~0414</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>1222679</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>5079</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>260415~0421</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>1181408</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>4412</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>260422~0428</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>1133506</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>4250</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>260429~0505</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>961336</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>3112</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>260506~0512</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>1137772</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>3832</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>260513~0519</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>1144297</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>3860</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>260520~0526</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>1128893</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>3771</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>260527~0602</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>1092317</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>3563</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>260603~0609</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>1120676</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>3894</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>260610~0616</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>1173816</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>4319</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>260617~0623</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>1091688</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>3623</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>260624~0630</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>1143963</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>3810</v>
       </c>
     </row>
   </sheetData>
@@ -3748,7 +8701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3776,104 +8729,247 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>912002</v>
+        <v>665617</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3956</v>
+        <v>2617</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>978657</v>
+        <v>731538</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>5432</v>
+        <v>2986</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1000981</v>
+        <v>753501</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>5484</v>
+        <v>3153</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1201377</v>
+        <v>873179</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>6191</v>
+        <v>4301</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1168320</v>
+        <v>785889</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4585</v>
+        <v>3276</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1078028</v>
+        <v>787518</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3569</v>
+        <v>3310</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1136915</v>
+        <v>774837</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>3909</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>774887</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>3279</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>833886</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>3734</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>902455</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>3917</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>928905</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>3771</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>912002</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>3956</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>978657</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>5432</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>1000981</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>5484</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>1201377</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>6191</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>1168320</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>4585</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>1078028</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>3569</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>1136915</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>3909</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B20" s="3" t="n">
         <v>1075816</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C20" s="3" t="n">
         <v>3403</v>
       </c>
     </row>
